--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N119_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N119_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>68.08303076425177</v>
+        <v>11.06349249919091</v>
       </c>
       <c r="D2" t="n">
-        <v>68.94114294532758</v>
+        <v>11.20293572861573</v>
       </c>
       <c r="E2" t="n">
-        <v>13.92336152055324</v>
+        <v>2.262546247089902</v>
       </c>
       <c r="F2" t="n">
-        <v>14.10499638535006</v>
+        <v>2.292061912619385</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>36.3532297310872</v>
+        <v>5.907399831301671</v>
       </c>
       <c r="D3" t="n">
-        <v>35.84274130928677</v>
+        <v>5.824445462759099</v>
       </c>
       <c r="E3" t="n">
-        <v>13.92336152055324</v>
+        <v>2.262546247089902</v>
       </c>
       <c r="F3" t="n">
-        <v>14.10499638535006</v>
+        <v>2.292061912619385</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>50.11205557950847</v>
+        <v>8.143209031670127</v>
       </c>
       <c r="D4" t="n">
-        <v>49.52236758802648</v>
+        <v>8.047384733054304</v>
       </c>
       <c r="E4" t="n">
-        <v>13.92336152055324</v>
+        <v>2.262546247089902</v>
       </c>
       <c r="F4" t="n">
-        <v>14.10499638535006</v>
+        <v>2.292061912619385</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>70.4578692203263</v>
+        <v>11.44940374830303</v>
       </c>
       <c r="D5" t="n">
-        <v>69.41918618514973</v>
+        <v>11.28061775508683</v>
       </c>
       <c r="E5" t="n">
-        <v>13.92336152055324</v>
+        <v>2.262546247089902</v>
       </c>
       <c r="F5" t="n">
-        <v>14.10499638535006</v>
+        <v>2.292061912619385</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
